--- a/batch_summary/summary_report/Pass_Fail_Summary.xlsx
+++ b/batch_summary/summary_report/Pass_Fail_Summary.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>99.77</v>
+        <v>99.61</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Preprocessing applied (restored 7 column(s), re-linked 2 primary key(s), repaired 7/8 foreign key(s), 1 FK(s) unfixable from source); fidelity 98.15% → 99.77% (+1.62). | Still below the 100.00% target after preprocessing; held in 2_preprocessed for review.</t>
+          <t>Preprocessing applied (restored 7 column(s), re-linked 2 primary key(s), repaired 7/8 foreign key(s), 1 FK(s) unfixable from source); fidelity 98.00% → 99.61% (+1.61). | NOT promoted — held in 2_preprocessed for review. Blocked by: 4 WARNING finding(s) awaiting human sign-off; measured fidelity 99.6101% is below the 100.00% target.</t>
         </is>
       </c>
     </row>

--- a/batch_summary/summary_report/Pass_Fail_Summary.xlsx
+++ b/batch_summary/summary_report/Pass_Fail_Summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Status Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,17 +438,72 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Fidelity %</t>
+          <t>V1 Fidelity %</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>V2 Fidelity %</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>V3 Fidelity %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Structural Fidelity %</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Documentation Fidelity %</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>UDP Fidelity % (XML)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>UDP Migration Pass Rate %</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>UDP Stage</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Report Folder</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>V1 Report</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>V2 Report</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>V3 Report</t>
         </is>
       </c>
     </row>
@@ -465,14 +520,69 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>65.63</v>
+      </c>
+      <c r="E2" t="n">
+        <v>98.97</v>
+      </c>
+      <c r="F2" t="n">
+        <v>98.97</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3_final</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PASS: overall fidelity 98.97% &gt;= 90.00% threshold (structural status was WARN: 0 CRITICAL, 10 WARNING finding(s) remain listed on the FINDINGS sheet)</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>98.45</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>EXTRACTED</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>app\reporting\ldm_reports\03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_V1_Initial_Fidelity_Report.xlsx</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_V2_UDP_Mapping_Report.xlsx</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_V3_Final_Fidelity_Report.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -487,14 +597,65 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>47.59</v>
+      </c>
+      <c r="E3" t="n">
+        <v>71.12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3_final</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PASS: overall fidelity 96.12% &gt;= 90.00% threshold (structural status was WARN: 0 CRITICAL, 64 WARNING finding(s) remain listed on the FINDINGS sheet)</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>92.23999999999999</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>100</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>COMPARED</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>app\reporting\cdm_reports\02_logistics_segment</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>02_logistics_segment_V1_Initial_Fidelity_Report.xlsx</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>02_logistics_segment_V2_UDP_Mapping_Report.xlsx</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>02_logistics_segment_V3_Final_Fidelity_Report.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -509,20 +670,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>99.77</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2_preprocessed</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Preprocessing applied (restored 7 column(s), re-linked 2 primary key(s), repaired 7/8 foreign key(s), 1 FK(s) unfixable from source); fidelity 98.15% → 99.77% (+1.62). | Still below the 100.00% target after preprocessing; held in 2_preprocessed for review.</t>
+        <v>73.67</v>
+      </c>
+      <c r="E4" t="n">
+        <v>74.31</v>
+      </c>
+      <c r="F4" t="n">
+        <v>99.31</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3_final</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Preprocessing applied (restored 7 column(s), re-linked 2 primary key(s), repaired 7/8 foreign key(s), 1 FK(s) unfixable from source); fidelity 73.67% → 99.31% (+25.64). | Promoted to 3_final.</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="J4" t="n">
+        <v>98.03</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>COMPARED</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>app\reporting\pdm_reports\05_Carbon_Calculator</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>05_Carbon_Calculator_V1_Initial_Fidelity_Report.xlsx</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>05_Carbon_Calculator_V2_UDP_Mapping_Report.xlsx</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>05_Carbon_Calculator_V3_Final_Fidelity_Report.xlsx</t>
         </is>
       </c>
     </row>

--- a/batch_summary/summary_report/Pass_Fail_Summary.xlsx
+++ b/batch_summary/summary_report/Pass_Fail_Summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Status Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -680,7 +680,7 @@
         <v>74.31</v>
       </c>
       <c r="F4" t="n">
-        <v>99.31</v>
+        <v>98.52</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Preprocessing applied (restored 7 column(s), re-linked 2 primary key(s), repaired 7/8 foreign key(s), 1 FK(s) unfixable from source); fidelity 73.67% → 99.31% (+25.64). | Promoted to 3_final.</t>
+          <t>Preprocessing applied (restored 7 column(s), re-linked 2 primary key(s), repaired 7/8 foreign key(s), 1 FK(s) unfixable from source); fidelity 73.67% → 98.52% (+24.85). | Promoted to 3_final.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>96.84</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>

--- a/batch_summary/summary_report/Pass_Fail_Summary.xlsx
+++ b/batch_summary/summary_report/Pass_Fail_Summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Status Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/batch_summary/summary_report/Pass_Fail_Summary.xlsx
+++ b/batch_summary/summary_report/Pass_Fail_Summary.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,17 +438,72 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Fidelity %</t>
+          <t>V1 Fidelity %</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>V2 Fidelity %</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>V3 Fidelity %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Structural Fidelity %</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Documentation Fidelity %</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>UDP Fidelity % (XML)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>UDP Migration Pass Rate %</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>UDP Stage</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Report Folder</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>V1 Report</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>V2 Report</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>V3 Report</t>
         </is>
       </c>
     </row>
@@ -465,14 +520,69 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>65.63</v>
+      </c>
+      <c r="E2" t="n">
+        <v>98.97</v>
+      </c>
+      <c r="F2" t="n">
+        <v>98.97</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3_final</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PASS: overall fidelity 98.97% &gt;= 90.00% threshold (structural status was WARN: 0 CRITICAL, 10 WARNING finding(s) remain listed on the FINDINGS sheet)</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>98.45</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>EXTRACTED</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>app\reporting\ldm_reports\03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_V1_Initial_Fidelity_Report.xlsx</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_V2_UDP_Mapping_Report.xlsx</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_V3_Final_Fidelity_Report.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -487,14 +597,65 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>47.59</v>
+      </c>
+      <c r="E3" t="n">
+        <v>71.12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3_final</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PASS: overall fidelity 96.12% &gt;= 90.00% threshold (structural status was WARN: 0 CRITICAL, 64 WARNING finding(s) remain listed on the FINDINGS sheet)</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>92.23999999999999</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>100</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>COMPARED</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>app\reporting\cdm_reports\02_logistics_segment</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>02_logistics_segment_V1_Initial_Fidelity_Report.xlsx</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>02_logistics_segment_V2_UDP_Mapping_Report.xlsx</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>02_logistics_segment_V3_Final_Fidelity_Report.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -509,20 +670,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>99.77</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2_preprocessed</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Preprocessing applied (restored 7 column(s), re-linked 2 primary key(s), repaired 7/8 foreign key(s), 1 FK(s) unfixable from source); fidelity 98.15% → 99.77% (+1.62). | Still below the 100.00% target after preprocessing; held in 2_preprocessed for review.</t>
+        <v>73.67</v>
+      </c>
+      <c r="E4" t="n">
+        <v>74.31</v>
+      </c>
+      <c r="F4" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3_final</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Preprocessing applied (restored 7 column(s), re-linked 2 primary key(s), repaired 7/8 foreign key(s), 1 FK(s) unfixable from source); fidelity 73.67% → 98.52% (+24.85). | Promoted to 3_final.</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="J4" t="n">
+        <v>98.03</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>COMPARED</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>app\reporting\pdm_reports\05_Carbon_Calculator</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>05_Carbon_Calculator_V1_Initial_Fidelity_Report.xlsx</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>05_Carbon_Calculator_V2_UDP_Mapping_Report.xlsx</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>05_Carbon_Calculator_V3_Final_Fidelity_Report.xlsx</t>
         </is>
       </c>
     </row>
